--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_012.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_012.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43E83F0B-AC47-4DA0-82FF-A1D965B7D1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0AEF4BE-CE46-4945-A4CF-590D5C262F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,13 +561,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S03aH02,S02aH02,S04aH02</t>
+    <t>S02aH02,S04aH02,S03aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S03aH01,S02aH01</t>
+    <t>S03aH01,S01aH01,S04aH01,S02aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S03aH01,S02aH01</v>
+        <v>S03aH01,S01aH01,S04aH01,S02aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH02,S03aH02,S02aH02,S04aH02</v>
+        <v>S02aH02,S04aH02,S03aH02,S01aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1290,7 +1290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A273015-6362-4696-8393-FF54E6902735}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A2FA57-6165-4E77-A0BD-79DBE5FF8890}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1368,7 +1368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388A6D30-74D4-4881-917F-03CADC5EFF97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16CD878-F8C6-4CA7-B043-AEB34A5C2083}">
   <dimension ref="B9:O170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6550,7 +6550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5FE4FD-8BA9-4251-9904-B8D37AF5E97C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B535A69-FF14-406A-93C2-C80EAC8F9FF6}">
   <dimension ref="B9:AV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10443,7 +10443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B68A37E-9C55-4165-8607-4EC543DD4B12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4914B8-6C26-4B12-B00C-412122AF257B}">
   <dimension ref="B9:E18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10585,7 +10585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFFB3F8-7368-48A1-93A1-9E328B5F76D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54179520-3670-4763-B116-70510AB96733}">
   <dimension ref="B9:D26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10788,7 +10788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D67C57-95D2-4643-B648-8455433F8F9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CD5E8F-4948-4531-9CE0-3647B7B0EBBF}">
   <dimension ref="B9:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10903,7 +10903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D5FCEC-98F3-435B-94E3-5B4171CAAA0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A073928-A230-405B-8878-2AAC8767FC69}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11033,7 +11033,7 @@
         <v>44</v>
       </c>
       <c r="D18">
-        <v>0.18325000000000002</v>
+        <v>0.18325</v>
       </c>
       <c r="E18" t="s">
         <v>181</v>
@@ -11243,7 +11243,7 @@
         <v>43</v>
       </c>
       <c r="D33">
-        <v>0.23651428571428568</v>
+        <v>0.2365142857142857</v>
       </c>
       <c r="E33" t="s">
         <v>181</v>
@@ -11313,7 +11313,7 @@
         <v>44</v>
       </c>
       <c r="D38">
-        <v>0.22297499999999998</v>
+        <v>0.22297500000000001</v>
       </c>
       <c r="E38" t="s">
         <v>181</v>
@@ -11425,7 +11425,7 @@
         <v>44</v>
       </c>
       <c r="D46">
-        <v>0.24877499999999997</v>
+        <v>0.248775</v>
       </c>
       <c r="E46" t="s">
         <v>181</v>
@@ -11467,7 +11467,7 @@
         <v>43</v>
       </c>
       <c r="D49">
-        <v>0.2512571428571429</v>
+        <v>0.25125714285714285</v>
       </c>
       <c r="E49" t="s">
         <v>181</v>
@@ -11523,7 +11523,7 @@
         <v>43</v>
       </c>
       <c r="D53">
-        <v>0.26035714285714284</v>
+        <v>0.2603571428571429</v>
       </c>
       <c r="E53" t="s">
         <v>181</v>
@@ -11537,7 +11537,7 @@
         <v>44</v>
       </c>
       <c r="D54">
-        <v>0.25419999999999998</v>
+        <v>0.25420000000000004</v>
       </c>
       <c r="E54" t="s">
         <v>181</v>
@@ -11649,7 +11649,7 @@
         <v>44</v>
       </c>
       <c r="D62">
-        <v>0.2213</v>
+        <v>0.22130000000000002</v>
       </c>
       <c r="E62" t="s">
         <v>181</v>
@@ -11705,7 +11705,7 @@
         <v>44</v>
       </c>
       <c r="D66">
-        <v>0.20402499999999998</v>
+        <v>0.20402500000000001</v>
       </c>
       <c r="E66" t="s">
         <v>181</v>
@@ -11929,7 +11929,7 @@
         <v>44</v>
       </c>
       <c r="D82">
-        <v>0.213975</v>
+        <v>0.21397499999999997</v>
       </c>
       <c r="E82" t="s">
         <v>181</v>
@@ -11985,7 +11985,7 @@
         <v>44</v>
       </c>
       <c r="D86">
-        <v>0.23290000000000002</v>
+        <v>0.2329</v>
       </c>
       <c r="E86" t="s">
         <v>181</v>
@@ -12027,7 +12027,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.27848571428571434</v>
+        <v>0.27848571428571428</v>
       </c>
       <c r="E89" t="s">
         <v>181</v>
@@ -12097,7 +12097,7 @@
         <v>44</v>
       </c>
       <c r="D94">
-        <v>0.23267499999999999</v>
+        <v>0.23267500000000002</v>
       </c>
       <c r="E94" t="s">
         <v>181</v>
@@ -12153,7 +12153,7 @@
         <v>44</v>
       </c>
       <c r="D98">
-        <v>0.23327499999999998</v>
+        <v>0.23327500000000001</v>
       </c>
       <c r="E98" t="s">
         <v>181</v>
@@ -12251,7 +12251,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.24881428571428571</v>
+        <v>0.24881428571428568</v>
       </c>
       <c r="E105" t="s">
         <v>181</v>
@@ -12321,7 +12321,7 @@
         <v>44</v>
       </c>
       <c r="D110">
-        <v>0.26190000000000002</v>
+        <v>0.26189999999999997</v>
       </c>
       <c r="E110" t="s">
         <v>181</v>
@@ -12419,7 +12419,7 @@
         <v>43</v>
       </c>
       <c r="D117">
-        <v>0.25347142857142857</v>
+        <v>0.25347142857142863</v>
       </c>
       <c r="E117" t="s">
         <v>181</v>
@@ -12433,7 +12433,7 @@
         <v>44</v>
       </c>
       <c r="D118">
-        <v>0.23932499999999998</v>
+        <v>0.23932500000000001</v>
       </c>
       <c r="E118" t="s">
         <v>181</v>
